--- a/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2003_2014/tabelas/diagnosticos_residuos.xlsx
+++ b/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2003_2014/tabelas/diagnosticos_residuos.xlsx
@@ -485,16 +485,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>628.4108393973879</v>
+        <v>628.4108393973886</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004583709280182018</v>
+        <v>0.004583709280181762</v>
       </c>
       <c r="E2" t="n">
-        <v>455.9549944297435</v>
+        <v>456.3264003028722</v>
       </c>
       <c r="F2" t="n">
-        <v>1.959661173716867e-88</v>
+        <v>1.635473336220935e-88</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -529,10 +529,10 @@
         <v>0.3386292735391778</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9710437327863596</v>
+        <v>0.9710437327863642</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4088560392668226</v>
+        <v>0.4088560392668208</v>
       </c>
     </row>
     <row r="4">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.860391592545836</v>
+        <v>2.860391592545852</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4136546305274874</v>
+        <v>0.4136546305274851</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8223083636025558</v>
+        <v>0.8223083636025604</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4840223105881317</v>
+        <v>0.4840223105881292</v>
       </c>
     </row>
     <row r="5">
@@ -589,16 +589,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4758497029858406</v>
+        <v>0.4758497029859037</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9241641742068278</v>
+        <v>0.9241641742068142</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1344928627339395</v>
+        <v>0.1344928627339401</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9393167572191244</v>
+        <v>0.9393167572191239</v>
       </c>
     </row>
     <row r="6">
@@ -622,16 +622,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6.724296440498824</v>
+        <v>6.724296440498871</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08122434855056271</v>
+        <v>0.0812243485505612</v>
       </c>
       <c r="J6" t="n">
-        <v>1.988323479697468</v>
+        <v>1.988323479697497</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1193723289730998</v>
+        <v>0.1193723289730955</v>
       </c>
     </row>
     <row r="7">
@@ -651,20 +651,20 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>39.17345398388753</v>
+        <v>1.603235371308976</v>
       </c>
       <c r="I7" t="n">
-        <v>1.594845586154259e-08</v>
+        <v>0.6586564436470428</v>
       </c>
       <c r="J7" t="n">
-        <v>15.2386540252939</v>
+        <v>0.4567727398986867</v>
       </c>
       <c r="K7" t="n">
-        <v>1.830873565265354e-08</v>
+        <v>0.7130041584953644</v>
       </c>
     </row>
     <row r="8">
@@ -684,20 +684,20 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.603235371308929</v>
+        <v>39.17345398388753</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6586564436470537</v>
+        <v>1.594845586154259e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4567727398986832</v>
+        <v>15.23865402529389</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7130041584953668</v>
+        <v>1.830873565265381e-08</v>
       </c>
     </row>
     <row r="9">
@@ -721,16 +721,16 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4.052275960064808</v>
+        <v>4.05227596006484</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2558743190605786</v>
+        <v>0.2558743190605751</v>
       </c>
       <c r="J9" t="n">
-        <v>1.175017852093512</v>
+        <v>1.175017852093508</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3222356261315139</v>
+        <v>0.322235626131515</v>
       </c>
     </row>
     <row r="10">
@@ -745,16 +745,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>614.6533317949159</v>
+        <v>614.6533317949157</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01305692541042279</v>
+        <v>0.0130569254104229</v>
       </c>
       <c r="E10" t="n">
-        <v>460.7999661194028</v>
+        <v>460.594442087031</v>
       </c>
       <c r="F10" t="n">
-        <v>1.851523517014277e-89</v>
+        <v>2.046448744066812e-89</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -789,10 +789,10 @@
         <v>0.1692386259751018</v>
       </c>
       <c r="J11" t="n">
-        <v>1.470505322543245</v>
+        <v>1.470505322543238</v>
       </c>
       <c r="K11" t="n">
-        <v>0.22603864471944</v>
+        <v>0.2260386447194419</v>
       </c>
     </row>
     <row r="12">
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.022963343350598</v>
+        <v>2.022963343350582</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5676542829493791</v>
+        <v>0.5676542829493825</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5780843463096607</v>
+        <v>0.5780843463096647</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6305098541683447</v>
+        <v>0.6305098541683423</v>
       </c>
     </row>
     <row r="13">
@@ -849,16 +849,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.4250944099862595</v>
+        <v>0.4250944099861964</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9350111579781024</v>
+        <v>0.9350111579781156</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1201044516228797</v>
+        <v>0.1201044516228772</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9481223005737802</v>
+        <v>0.9481223005737818</v>
       </c>
     </row>
     <row r="14">
@@ -888,10 +888,10 @@
         <v>0.3602265178870684</v>
       </c>
       <c r="J14" t="n">
-        <v>0.925426559867783</v>
+        <v>0.9254265598677821</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4307901111337038</v>
+        <v>0.4307901111337044</v>
       </c>
     </row>
     <row r="15">
@@ -911,20 +911,20 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>38.42835201800124</v>
+        <v>3.001253656501733</v>
       </c>
       <c r="I15" t="n">
-        <v>2.293746274339148e-08</v>
+        <v>0.3914319274817491</v>
       </c>
       <c r="J15" t="n">
-        <v>14.84126313204182</v>
+        <v>0.8636779065862674</v>
       </c>
       <c r="K15" t="n">
-        <v>2.798091789667941e-08</v>
+        <v>0.4620513713074451</v>
       </c>
     </row>
     <row r="16">
@@ -944,20 +944,20 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3.001253656501702</v>
+        <v>38.42835201800129</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3914319274817521</v>
+        <v>2.293746274339087e-08</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8636779065862538</v>
+        <v>14.84126313204186</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4620513713074523</v>
+        <v>2.798091789667812e-08</v>
       </c>
     </row>
     <row r="17">
@@ -987,10 +987,10 @@
         <v>0.08025108449013946</v>
       </c>
       <c r="J17" t="n">
-        <v>1.996799217708501</v>
+        <v>1.996799217708496</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1181169771135347</v>
+        <v>0.1181169771135355</v>
       </c>
     </row>
     <row r="18">
@@ -1005,16 +1005,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>646.3009709559382</v>
+        <v>646.3009709559395</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0009894864039417502</v>
+        <v>0.0009894864039416268</v>
       </c>
       <c r="E18" t="n">
-        <v>192.4747612846316</v>
+        <v>193.4173707585542</v>
       </c>
       <c r="F18" t="n">
-        <v>1.883699475242449e-33</v>
+        <v>1.210372862765128e-33</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1043,16 +1043,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.966096597469513</v>
+        <v>2.966096597469466</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3968820060683799</v>
+        <v>0.3968820060683871</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8533448388863999</v>
+        <v>0.8533448388863989</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4674614961772071</v>
+        <v>0.4674614961772079</v>
       </c>
     </row>
     <row r="20">
@@ -1076,16 +1076,16 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.777500331533587</v>
+        <v>2.77750033153365</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4272171684943536</v>
+        <v>0.4272171684943433</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7980032934756059</v>
+        <v>0.7980032934756308</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4973181290852567</v>
+        <v>0.497318129085243</v>
       </c>
     </row>
     <row r="21">
@@ -1109,16 +1109,16 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5.966119501085041</v>
+        <v>5.966119501085136</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1132702703492899</v>
+        <v>0.1132702703492851</v>
       </c>
       <c r="J21" t="n">
-        <v>1.754303995211743</v>
+        <v>1.754303995211747</v>
       </c>
       <c r="K21" t="n">
-        <v>0.15962161734679</v>
+        <v>0.1596216173467893</v>
       </c>
     </row>
     <row r="22">
@@ -1142,16 +1142,16 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>8.060281689693726</v>
+        <v>8.06028168969368</v>
       </c>
       <c r="I22" t="n">
-        <v>0.04478215560131532</v>
+        <v>0.04478215560131641</v>
       </c>
       <c r="J22" t="n">
-        <v>2.407137118511742</v>
+        <v>2.407137118511767</v>
       </c>
       <c r="K22" t="n">
-        <v>0.07058854073137708</v>
+        <v>0.07058854073137488</v>
       </c>
     </row>
     <row r="23">
@@ -1171,20 +1171,20 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>38.74960689123944</v>
+        <v>2.098387623814681</v>
       </c>
       <c r="I23" t="n">
-        <v>1.961130147273317e-08</v>
+        <v>0.5522390268939588</v>
       </c>
       <c r="J23" t="n">
-        <v>15.01189708805153</v>
+        <v>0.59996095489513</v>
       </c>
       <c r="K23" t="n">
-        <v>2.331400206465832e-08</v>
+        <v>0.616257391296866</v>
       </c>
     </row>
     <row r="24">
@@ -1204,20 +1204,20 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.098387623814571</v>
+        <v>38.74960689123944</v>
       </c>
       <c r="I24" t="n">
-        <v>0.552239026893981</v>
+        <v>1.961130147273317e-08</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5999609548951145</v>
+        <v>15.01189708805155</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6162573912968761</v>
+        <v>2.331400206465778e-08</v>
       </c>
     </row>
     <row r="25">
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>7.496151613879637</v>
+        <v>7.496151613879652</v>
       </c>
       <c r="I25" t="n">
-        <v>0.05765741596177214</v>
+        <v>0.05765741596177175</v>
       </c>
       <c r="J25" t="n">
-        <v>2.229274984715732</v>
+        <v>2.229274984715802</v>
       </c>
       <c r="K25" t="n">
-        <v>0.08829195971252234</v>
+        <v>0.08829195971251456</v>
       </c>
     </row>
     <row r="26">
@@ -1265,16 +1265,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>515.2079847356579</v>
+        <v>515.2079847356581</v>
       </c>
       <c r="D26" t="n">
-        <v>0.008354742250434276</v>
+        <v>0.008354742250434101</v>
       </c>
       <c r="E26" t="n">
-        <v>117.3939711255865</v>
+        <v>116.6281561836819</v>
       </c>
       <c r="F26" t="n">
-        <v>2.034769296147193e-18</v>
+        <v>2.871225862998981e-18</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1303,16 +1303,16 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3.239720842134426</v>
+        <v>3.239720842134504</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6630822687044849</v>
+        <v>0.6630822687044728</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4832565828799854</v>
+        <v>0.4832565828799907</v>
       </c>
       <c r="K27" t="n">
-        <v>0.7880500818333198</v>
+        <v>0.7880500818333162</v>
       </c>
     </row>
     <row r="28">
@@ -1336,16 +1336,16 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>10.57893382555408</v>
+        <v>10.57893382555401</v>
       </c>
       <c r="I28" t="n">
-        <v>0.06039803573108964</v>
+        <v>0.06039803573109104</v>
       </c>
       <c r="J28" t="n">
-        <v>1.667504807528118</v>
+        <v>1.667504807528107</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1491786569509426</v>
+        <v>0.1491786569509453</v>
       </c>
     </row>
     <row r="29">
@@ -1369,16 +1369,16 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>7.32627587968758</v>
+        <v>7.326275879687549</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1974834617463146</v>
+        <v>0.1974834617463169</v>
       </c>
       <c r="J29" t="n">
-        <v>1.126493048541364</v>
+        <v>1.126493048541362</v>
       </c>
       <c r="K29" t="n">
-        <v>0.351167264047198</v>
+        <v>0.3511672640471993</v>
       </c>
     </row>
     <row r="30">
@@ -1402,16 +1402,16 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>8.029398264958939</v>
+        <v>8.029398264958891</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1546228565674673</v>
+        <v>0.15462285656747</v>
       </c>
       <c r="J30" t="n">
-        <v>1.241183433671271</v>
+        <v>1.241183433671268</v>
       </c>
       <c r="K30" t="n">
-        <v>0.295462520443984</v>
+        <v>0.2954625204439853</v>
       </c>
     </row>
     <row r="31">
@@ -1431,20 +1431,20 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>10.54689772741342</v>
+        <v>8.267223479013841</v>
       </c>
       <c r="I31" t="n">
-        <v>0.06114173655933534</v>
+        <v>0.142110362749795</v>
       </c>
       <c r="J31" t="n">
-        <v>1.662043704338448</v>
+        <v>1.280253581727357</v>
       </c>
       <c r="K31" t="n">
-        <v>0.1505387897751528</v>
+        <v>0.2782245478458705</v>
       </c>
     </row>
     <row r="32">
@@ -1464,20 +1464,20 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>8.267223479013809</v>
+        <v>10.5468977274134</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1421103627497967</v>
+        <v>0.06114173655933583</v>
       </c>
       <c r="J32" t="n">
-        <v>1.280253581727357</v>
+        <v>1.66204370433845</v>
       </c>
       <c r="K32" t="n">
-        <v>0.2782245478458705</v>
+        <v>0.1505387897751526</v>
       </c>
     </row>
     <row r="33">
@@ -1501,16 +1501,16 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>10.20895008320928</v>
+        <v>10.20895008320922</v>
       </c>
       <c r="I33" t="n">
-        <v>0.06952665233666017</v>
+        <v>0.0695266523366619</v>
       </c>
       <c r="J33" t="n">
-        <v>1.60459894446486</v>
+        <v>1.604598944464854</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1655487034006168</v>
+        <v>0.1655487034006186</v>
       </c>
     </row>
     <row r="34">
@@ -1525,16 +1525,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>638.0458493446839</v>
+        <v>638.0458493446838</v>
       </c>
       <c r="D34" t="n">
-        <v>0.002055728139904555</v>
+        <v>0.002055728139904574</v>
       </c>
       <c r="E34" t="n">
-        <v>78.48323433678716</v>
+        <v>78.7761589913159</v>
       </c>
       <c r="F34" t="n">
-        <v>5.402487789822262e-11</v>
+        <v>4.768926603515116e-11</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -1563,16 +1563,16 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3.376298946309009</v>
+        <v>3.376298946308977</v>
       </c>
       <c r="I35" t="n">
-        <v>0.337163647129208</v>
+        <v>0.337163647129213</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9742342530593251</v>
+        <v>0.9742342530593179</v>
       </c>
       <c r="K35" t="n">
-        <v>0.4073582832669089</v>
+        <v>0.4073582832669125</v>
       </c>
     </row>
     <row r="36">
@@ -1596,16 +1596,16 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2.566764391245985</v>
+        <v>2.566764391245969</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4633459922729954</v>
+        <v>0.4633459922729982</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7363422013523965</v>
+        <v>0.7363422013524191</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5323393760639961</v>
+        <v>0.5323393760639825</v>
       </c>
     </row>
     <row r="37">
@@ -1629,16 +1629,16 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6.682362366377409</v>
+        <v>6.682362366377472</v>
       </c>
       <c r="I37" t="n">
-        <v>0.08274146292899889</v>
+        <v>0.08274146292899665</v>
       </c>
       <c r="J37" t="n">
-        <v>1.975311565657147</v>
+        <v>1.975311565657153</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1213248330868177</v>
+        <v>0.1213248330868169</v>
       </c>
     </row>
     <row r="38">
@@ -1668,10 +1668,10 @@
         <v>0.1388139834295091</v>
       </c>
       <c r="J38" t="n">
-        <v>1.61082835288833</v>
+        <v>1.610828352888307</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1904542566507144</v>
+        <v>0.1904542566507199</v>
       </c>
     </row>
     <row r="39">
@@ -1691,20 +1691,20 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>39.27020086962754</v>
+        <v>1.972141435666149</v>
       </c>
       <c r="I39" t="n">
-        <v>1.521319826980135e-08</v>
+        <v>0.5782089414177596</v>
       </c>
       <c r="J39" t="n">
-        <v>15.29067561780803</v>
+        <v>0.5633568793770042</v>
       </c>
       <c r="K39" t="n">
-        <v>1.732349500315568e-08</v>
+        <v>0.6402201832879493</v>
       </c>
     </row>
     <row r="40">
@@ -1724,20 +1724,20 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.972141435666102</v>
+        <v>39.27020086962745</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5782089414177698</v>
+        <v>1.521319826980204e-08</v>
       </c>
       <c r="J40" t="n">
-        <v>0.5633568793769818</v>
+        <v>15.29067561780798</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6402201832879639</v>
+        <v>1.732349500315654e-08</v>
       </c>
     </row>
     <row r="41">
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5.699699197377798</v>
+        <v>5.69969919737761</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1271704799977073</v>
+        <v>0.1271704799977179</v>
       </c>
       <c r="J41" t="n">
-        <v>1.672688662846422</v>
+        <v>1.672688662846405</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1765196407555395</v>
+        <v>0.1765196407555432</v>
       </c>
     </row>
     <row r="42">
@@ -1785,16 +1785,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>648.2684411600396</v>
+        <v>648.2684411600394</v>
       </c>
       <c r="D42" t="n">
-        <v>0.000826320438371113</v>
+        <v>0.0008263204383711309</v>
       </c>
       <c r="E42" t="n">
-        <v>79.91192618240777</v>
+        <v>80.31077496488419</v>
       </c>
       <c r="F42" t="n">
-        <v>2.938019504728567e-11</v>
+        <v>2.477774829356761e-11</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -1823,16 +1823,16 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>4.596762561105498</v>
+        <v>4.596762561105466</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2038199815545496</v>
+        <v>0.2038199815545522</v>
       </c>
       <c r="J43" t="n">
-        <v>1.338181733352442</v>
+        <v>1.33818173335244</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2652459062325576</v>
+        <v>0.2652459062325583</v>
       </c>
     </row>
     <row r="44">
@@ -1856,16 +1856,16 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2.496098102033693</v>
+        <v>2.49609810203374</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4759966564166939</v>
+        <v>0.4759966564166854</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7157070355951424</v>
+        <v>0.7157070355951465</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5444714034795459</v>
+        <v>0.5444714034795435</v>
       </c>
     </row>
     <row r="45">
@@ -1895,10 +1895,10 @@
         <v>0.06890305844451065</v>
       </c>
       <c r="J45" t="n">
-        <v>2.103984144849889</v>
+        <v>2.103984144849891</v>
       </c>
       <c r="K45" t="n">
-        <v>0.103310003734502</v>
+        <v>0.1033100037345018</v>
       </c>
     </row>
     <row r="46">
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2.107188301629407</v>
+        <v>2.107188301629375</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5504598904226738</v>
+        <v>0.5504598904226805</v>
       </c>
       <c r="J46" t="n">
-        <v>0.6025151045424192</v>
+        <v>0.6025151045424213</v>
       </c>
       <c r="K46" t="n">
-        <v>0.6146070083667252</v>
+        <v>0.6146070083667237</v>
       </c>
     </row>
     <row r="47">
@@ -1951,20 +1951,20 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>38.5162805777647</v>
+        <v>2.984242569969705</v>
       </c>
       <c r="I47" t="n">
-        <v>2.197476492090231e-08</v>
+        <v>0.3940610480020227</v>
       </c>
       <c r="J47" t="n">
-        <v>14.88786092838826</v>
+        <v>0.8586774981884328</v>
       </c>
       <c r="K47" t="n">
-        <v>2.661942150138017e-08</v>
+        <v>0.4646630132116472</v>
       </c>
     </row>
     <row r="48">
@@ -1984,20 +1984,20 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.984242569969736</v>
+        <v>38.51628057776466</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3940610480020179</v>
+        <v>2.197476492090279e-08</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8586774981884325</v>
+        <v>14.88786092838825</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4646630132116476</v>
+        <v>2.661942150138033e-08</v>
       </c>
     </row>
     <row r="49">
@@ -2021,16 +2021,16 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>7.54672966033635</v>
+        <v>7.546729660336287</v>
       </c>
       <c r="I49" t="n">
-        <v>0.05636984598471045</v>
+        <v>0.056369845984712</v>
       </c>
       <c r="J49" t="n">
-        <v>2.245160609711103</v>
+        <v>2.245160609711126</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0865478062049978</v>
+        <v>0.08654780620499536</v>
       </c>
     </row>
     <row r="50">
@@ -2045,16 +2045,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>633.5796549239187</v>
+        <v>633.5796549239204</v>
       </c>
       <c r="D50" t="n">
-        <v>0.003002040488976332</v>
+        <v>0.003002040488975907</v>
       </c>
       <c r="E50" t="n">
-        <v>401.2126236978397</v>
+        <v>401.2862942779512</v>
       </c>
       <c r="F50" t="n">
-        <v>7.041097892545595e-77</v>
+        <v>6.793897854985377e-77</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
@@ -2083,16 +2083,16 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2.471994298425799</v>
+        <v>2.471994298425847</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4803736084562327</v>
+        <v>0.480373608456224</v>
       </c>
       <c r="J51" t="n">
-        <v>0.7086732978074569</v>
+        <v>0.7086732978074538</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5486536533696731</v>
+        <v>0.5486536533696749</v>
       </c>
     </row>
     <row r="52">
@@ -2122,10 +2122,10 @@
         <v>0.509379920918136</v>
       </c>
       <c r="J52" t="n">
-        <v>0.6633375606356531</v>
+        <v>0.6633375606356579</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5761768653380379</v>
+        <v>0.576176865338035</v>
       </c>
     </row>
     <row r="53">
@@ -2155,10 +2155,10 @@
         <v>0.6081332482979287</v>
       </c>
       <c r="J53" t="n">
-        <v>0.5226179164124317</v>
+        <v>0.5226179164124293</v>
       </c>
       <c r="K53" t="n">
-        <v>0.6675431620355655</v>
+        <v>0.6675431620355674</v>
       </c>
     </row>
     <row r="54">
@@ -2182,16 +2182,16 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>8.011284204594201</v>
+        <v>8.011284204594169</v>
       </c>
       <c r="I54" t="n">
-        <v>0.04577906995188163</v>
+        <v>0.04577906995188236</v>
       </c>
       <c r="J54" t="n">
-        <v>2.391629521049218</v>
+        <v>2.391629521049213</v>
       </c>
       <c r="K54" t="n">
-        <v>0.07198160091649458</v>
+        <v>0.07198160091649498</v>
       </c>
     </row>
     <row r="55">
@@ -2211,20 +2211,20 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>38.41118079255109</v>
+        <v>2.087241920812336</v>
       </c>
       <c r="I55" t="n">
-        <v>2.313032342920575e-08</v>
+        <v>0.5544981186523568</v>
       </c>
       <c r="J55" t="n">
-        <v>14.83217246279372</v>
+        <v>0.5967266886786685</v>
       </c>
       <c r="K55" t="n">
-        <v>2.825466718996323e-08</v>
+        <v>0.618351360352569</v>
       </c>
     </row>
     <row r="56">
@@ -2244,20 +2244,20 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2.087241920812305</v>
+        <v>38.41118079255101</v>
       </c>
       <c r="I56" t="n">
-        <v>0.5544981186523632</v>
+        <v>2.313032342920661e-08</v>
       </c>
       <c r="J56" t="n">
-        <v>0.5967266886786554</v>
+        <v>14.83217246279372</v>
       </c>
       <c r="K56" t="n">
-        <v>0.6183513603525777</v>
+        <v>2.825466718996323e-08</v>
       </c>
     </row>
     <row r="57">
@@ -2281,16 +2281,16 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>4.664071622770035</v>
+        <v>4.664071622770004</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1981141092351198</v>
+        <v>0.1981141092351219</v>
       </c>
       <c r="J57" t="n">
-        <v>1.358441793893557</v>
+        <v>1.358441793893548</v>
       </c>
       <c r="K57" t="n">
-        <v>0.2588578232320313</v>
+        <v>0.258857823232034</v>
       </c>
     </row>
     <row r="58">
@@ -2305,16 +2305,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>634.0525847108556</v>
+        <v>634.0525847108555</v>
       </c>
       <c r="D58" t="n">
-        <v>0.002885686177042836</v>
+        <v>0.002885686177042854</v>
       </c>
       <c r="E58" t="n">
-        <v>413.8556471439132</v>
+        <v>413.5522788014092</v>
       </c>
       <c r="F58" t="n">
-        <v>1.522943655045678e-79</v>
+        <v>1.764647835608143e-79</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
@@ -2349,10 +2349,10 @@
         <v>0.3784080219917207</v>
       </c>
       <c r="J59" t="n">
-        <v>0.8888957978177832</v>
+        <v>0.8888957978177818</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4490639717151182</v>
+        <v>0.449063971715119</v>
       </c>
     </row>
     <row r="60">
@@ -2376,16 +2376,16 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1.977711320044647</v>
+        <v>1.977711320044679</v>
       </c>
       <c r="I60" t="n">
-        <v>0.5770456678788061</v>
+        <v>0.5770456678787994</v>
       </c>
       <c r="J60" t="n">
-        <v>0.5649704311190157</v>
+        <v>0.564970431119015</v>
       </c>
       <c r="K60" t="n">
-        <v>0.6391518646551515</v>
+        <v>0.6391518646551517</v>
       </c>
     </row>
     <row r="61">
@@ -2415,7 +2415,7 @@
         <v>0.4109101352099812</v>
       </c>
       <c r="J61" t="n">
-        <v>0.8273106712546866</v>
+        <v>0.8273106712546864</v>
       </c>
       <c r="K61" t="n">
         <v>0.4813215146244406</v>
@@ -2442,16 +2442,16 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.439889790538419</v>
+        <v>3.439889790538435</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3286423019807626</v>
+        <v>0.3286423019807622</v>
       </c>
       <c r="J62" t="n">
-        <v>0.9930389880141748</v>
+        <v>0.9930389880141691</v>
       </c>
       <c r="K62" t="n">
-        <v>0.3986260910780568</v>
+        <v>0.3986260910780594</v>
       </c>
     </row>
     <row r="63">
@@ -2471,20 +2471,20 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>38.6402408616443</v>
+        <v>3.742784172115242</v>
       </c>
       <c r="I63" t="n">
-        <v>2.068572331168158e-08</v>
+        <v>0.2906118018271825</v>
       </c>
       <c r="J63" t="n">
-        <v>14.95368843107349</v>
+        <v>1.082846678114681</v>
       </c>
       <c r="K63" t="n">
-        <v>2.480985924242416e-08</v>
+        <v>0.3591298188004994</v>
       </c>
     </row>
     <row r="64">
@@ -2504,20 +2504,20 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>3.742784172115195</v>
+        <v>38.64024086164433</v>
       </c>
       <c r="I64" t="n">
-        <v>0.29061180182719</v>
+        <v>2.068572331168128e-08</v>
       </c>
       <c r="J64" t="n">
-        <v>1.082846678114669</v>
+        <v>14.95368843107349</v>
       </c>
       <c r="K64" t="n">
-        <v>0.3591298188005046</v>
+        <v>2.480985924242416e-08</v>
       </c>
     </row>
     <row r="65">
@@ -2541,16 +2541,16 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>5.31752685788783</v>
+        <v>5.317526857887877</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1499691343790413</v>
+        <v>0.1499691343790387</v>
       </c>
       <c r="J65" t="n">
-        <v>1.556169342168415</v>
+        <v>1.556169342168419</v>
       </c>
       <c r="K65" t="n">
-        <v>0.2036329533043699</v>
+        <v>0.203632953304369</v>
       </c>
     </row>
   </sheetData>
